--- a/DateBase/orders/Nha Thu_2026-7-1.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-1.xlsx
@@ -521,6 +521,9 @@
       <c r="C11" t="str">
         <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
       </c>
+      <c r="F11" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -579,7 +582,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015965255510100</v>
+        <v>0159652555101015</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-1.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-1.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,9 +525,90 @@
         <v>15</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>105_绣球莫奈蓝_Hydrangea Monet Blue_Hydrangea L._1stem</v>
+      </c>
+      <c r="F12" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>122_绣球拇指薄荷_Hydrangea_Hydrangea L._1stem</v>
+      </c>
+      <c r="F13" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>119_绣球璀璨_Hydrangea_Hydrangea L._1stem</v>
+      </c>
+      <c r="F14" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>874_小菊科隆香水_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>84_堪培拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="C20" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,7 +663,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0159652555101015</v>
+        <v>0159652555101015157121010101510250</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-1.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-1.xlsx
@@ -605,6 +605,9 @@
       <c r="A21" t="str">
         <v>3</v>
       </c>
+      <c r="C21" t="str">
+        <v>770_小弯葱_undefined_undefined_10stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-7-1.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-1.xlsx
@@ -608,6 +608,9 @@
       <c r="C21" t="str">
         <v>770_小弯葱_undefined_undefined_10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -666,7 +669,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0159652555101015157121010101510250</v>
+        <v>01596525551010151571210101015102510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-1.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-1.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -612,9 +612,17 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>747_乒乓菊绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L22"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -669,7 +677,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01596525551010151571210101015102510</v>
+        <v>015965255510101515712101010151025105</v>
       </c>
     </row>
   </sheetData>
